--- a/plm python control/wrappers/multibeam parameters/multiBeam_BeamA_100_BeamB_100.xlsx
+++ b/plm python control/wrappers/multibeam parameters/multiBeam_BeamA_100_BeamB_100.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3330" yWindow="1950" windowWidth="7260" windowHeight="11505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,6 +414,9 @@
   </sheetPr>
   <dimension ref="A1:D539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
@@ -431,7 +434,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.27609427609428</v>
+        <v>11.041366041366</v>
       </c>
     </row>
     <row r="3">
@@ -449,7 +452,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.65656565656566</v>
+        <v>11.9450456950457</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +470,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91.16</v>
+        <v>38.11199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +488,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.5375</v>
+        <v>11.806</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +506,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +596,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.501681768714213</v>
+        <v>0.860942390479872</v>
       </c>
     </row>
     <row r="12"/>
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2090602999694</v>
+        <v>10.76866395191003</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +633,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.99326599326599</v>
+        <v>11.14989334884623</v>
       </c>
     </row>
     <row r="15">
@@ -648,7 +651,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.94</v>
+        <v>35.072</v>
       </c>
     </row>
     <row r="16">
@@ -666,7 +669,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.865</v>
+        <v>11.017</v>
       </c>
     </row>
     <row r="17">
@@ -684,7 +687,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46.8</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="18">
@@ -774,7 +777,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.175913003653173</v>
+        <v>1.510315140465751</v>
       </c>
     </row>
     <row r="23"/>
@@ -793,7 +796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.17441077441077</v>
+        <v>13.00733220530175</v>
       </c>
     </row>
     <row r="25">
@@ -811,7 +814,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.35185185185185</v>
+        <v>13.06542583192329</v>
       </c>
     </row>
     <row r="26">
@@ -829,7 +832,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>86.45999999999999</v>
+        <v>80.02</v>
       </c>
     </row>
     <row r="27">
@@ -847,7 +850,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.214</v>
+        <v>12.8845</v>
       </c>
     </row>
     <row r="28">
@@ -865,7 +868,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="29">
@@ -955,7 +958,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.092709955054622</v>
+        <v>0.9977122984440414</v>
       </c>
     </row>
     <row r="34"/>
@@ -974,7 +977,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.92547834843907</v>
+        <v>11.8972520908005</v>
       </c>
     </row>
     <row r="36">
@@ -992,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.56394763343404</v>
+        <v>10.8990442054958</v>
       </c>
     </row>
     <row r="37">
@@ -1010,7 +1013,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>51.38</v>
+        <v>50.792</v>
       </c>
     </row>
     <row r="38">
@@ -1028,7 +1031,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4405</v>
+        <v>10.7665</v>
       </c>
     </row>
     <row r="39">
@@ -1046,7 +1049,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="40">
@@ -1136,7 +1139,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.308016473348828</v>
+        <v>0.7991321069172165</v>
       </c>
     </row>
     <row r="45"/>
@@ -1155,7 +1158,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.66666666666667</v>
+        <v>11.0213571235469</v>
       </c>
     </row>
     <row r="47">
@@ -1173,7 +1176,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.77777777777778</v>
+        <v>12.3702351987023</v>
       </c>
     </row>
     <row r="48">
@@ -1191,7 +1194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>34.09200000000001</v>
+        <v>37.932</v>
       </c>
     </row>
     <row r="49">
@@ -1209,7 +1212,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.615</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="50">
@@ -1317,7 +1320,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.121893567608575</v>
+        <v>0.9767341228705003</v>
       </c>
     </row>
     <row r="56"/>
@@ -1336,7 +1339,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.7109144542773</v>
+        <v>11.4966532797858</v>
       </c>
     </row>
     <row r="58">
@@ -1354,7 +1357,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.9203539823009</v>
+        <v>10.8762829094154</v>
       </c>
     </row>
     <row r="59">
@@ -1372,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>47.472</v>
+        <v>44.172</v>
       </c>
     </row>
     <row r="60">
@@ -1390,7 +1393,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.7325</v>
+        <v>10.741</v>
       </c>
     </row>
     <row r="61">
@@ -1408,7 +1411,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>50.4</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="62">
@@ -1498,7 +1501,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.423865364731862</v>
+        <v>0.9412472481745967</v>
       </c>
     </row>
     <row r="67"/>
@@ -1517,7 +1520,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.82486662027372</v>
+        <v>11.4657315122431</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1538,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.48248666202737</v>
+        <v>11.2212378491448</v>
       </c>
     </row>
     <row r="70">
@@ -1553,7 +1556,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>35.712</v>
+        <v>43.752</v>
       </c>
     </row>
     <row r="71">
@@ -1571,7 +1574,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.3635</v>
+        <v>11.0875</v>
       </c>
     </row>
     <row r="72">
@@ -1589,7 +1592,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="73">
@@ -1679,7 +1682,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3.603323344414065</v>
+        <v>0.8469196542466461</v>
       </c>
     </row>
     <row r="78"/>
@@ -1698,7 +1701,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.79142300194932</v>
+        <v>11.0763603109282</v>
       </c>
     </row>
     <row r="80">
@@ -1716,7 +1719,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.63840155945419</v>
+        <v>11.5512117055327</v>
       </c>
     </row>
     <row r="81">
@@ -1734,7 +1737,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>72.23999999999999</v>
+        <v>38.532</v>
       </c>
     </row>
     <row r="82">
@@ -1752,7 +1755,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.5175</v>
+        <v>11.4145</v>
       </c>
     </row>
     <row r="83">
@@ -1770,7 +1773,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>43</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="84">
@@ -1860,7 +1863,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.336042199922222</v>
+        <v>0.9552585633617423</v>
       </c>
     </row>
     <row r="89"/>
@@ -1879,7 +1882,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.7468671679198</v>
+        <v>12.30681003584229</v>
       </c>
     </row>
     <row r="91">
@@ -1897,7 +1900,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.97257031467558</v>
+        <v>10.92712066905615</v>
       </c>
     </row>
     <row r="92">
@@ -1915,7 +1918,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>71.04000000000001</v>
+        <v>59.212</v>
       </c>
     </row>
     <row r="93">
@@ -1933,7 +1936,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.842</v>
+        <v>10.7975</v>
       </c>
     </row>
     <row r="94">
@@ -1951,7 +1954,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>41.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95">
@@ -2041,7 +2044,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.9649315196531154</v>
+        <v>0.8202330471954068</v>
       </c>
     </row>
     <row r="100"/>
@@ -2060,7 +2063,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8576306803257</v>
+        <v>13.04970255229323</v>
       </c>
     </row>
     <row r="102">
@@ -2078,7 +2081,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.24573154715</v>
+        <v>12.58779504893495</v>
       </c>
     </row>
     <row r="103">
@@ -2096,7 +2099,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>50.212</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -2114,7 +2117,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.11</v>
+        <v>12.4185</v>
       </c>
     </row>
     <row r="105">
@@ -2132,7 +2135,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>36.2</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="106">
@@ -2222,7 +2225,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.3693450784513247</v>
+        <v>0.8168169605027884</v>
       </c>
     </row>
     <row r="111"/>
@@ -2241,7 +2244,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.996996996997</v>
+        <v>13.27609427609428</v>
       </c>
     </row>
     <row r="113">
@@ -2259,7 +2262,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.8328328328328</v>
+        <v>10.65656565656566</v>
       </c>
     </row>
     <row r="114">
@@ -2277,7 +2280,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>37.652</v>
+        <v>91.16</v>
       </c>
     </row>
     <row r="115">
@@ -2295,7 +2298,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.667</v>
+        <v>10.5375</v>
       </c>
     </row>
     <row r="116">
@@ -2313,7 +2316,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>36.8</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="117">
@@ -2403,7 +2406,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2.975226561528034</v>
+        <v>0.9542779506156607</v>
       </c>
     </row>
     <row r="122"/>
@@ -2422,7 +2425,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>12.79142300194932</v>
+        <v>11.8156028368794</v>
       </c>
     </row>
     <row r="124">
@@ -2440,7 +2443,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.63840155945419</v>
+        <v>11.613475177305</v>
       </c>
     </row>
     <row r="125">
@@ -2458,7 +2461,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>72.23999999999999</v>
+        <v>49.372</v>
       </c>
     </row>
     <row r="126">
@@ -2476,7 +2479,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.5175</v>
+        <v>11.469</v>
       </c>
     </row>
     <row r="127">
@@ -2494,7 +2497,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>43</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="128">
@@ -2584,7 +2587,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2.899275493905002</v>
+        <v>0.8536104136689487</v>
       </c>
     </row>
     <row r="133"/>
@@ -2603,7 +2606,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.4657315122431</v>
+        <v>12.1895596383785</v>
       </c>
     </row>
     <row r="135">
@@ -2621,7 +2624,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.2212378491448</v>
+        <v>12.0450568678915</v>
       </c>
     </row>
     <row r="136">
@@ -2639,7 +2642,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>43.752</v>
+        <v>56.612</v>
       </c>
     </row>
     <row r="137">
@@ -2657,7 +2660,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.0875</v>
+        <v>11.885</v>
       </c>
     </row>
     <row r="138">
@@ -2675,7 +2678,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>37.4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="139">
@@ -2765,7 +2768,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.5384833351585951</v>
+        <v>0.6148732509749562</v>
       </c>
     </row>
     <row r="144"/>
@@ -2784,7 +2787,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>12.54716981132075</v>
+        <v>13.0872567482737</v>
       </c>
     </row>
     <row r="146">
@@ -2802,7 +2805,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>13.01712089447939</v>
+        <v>12.13826114249843</v>
       </c>
     </row>
     <row r="147">
@@ -2820,7 +2823,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>65.13199999999999</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="148">
@@ -2838,7 +2841,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>12.8285</v>
+        <v>11.981</v>
       </c>
     </row>
     <row r="149">
@@ -2856,7 +2859,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>55.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="150">
@@ -2946,7 +2949,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1.118828454436248</v>
+        <v>0.7451492124758263</v>
       </c>
     </row>
     <row r="155"/>
@@ -2965,7 +2968,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>10.79717813051146</v>
+        <v>13.2090602999694</v>
       </c>
     </row>
     <row r="157">
@@ -2983,7 +2986,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>10.81128747795414</v>
+        <v>10.99326599326599</v>
       </c>
     </row>
     <row r="158">
@@ -3001,7 +3004,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>35.372</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="159">
@@ -3019,7 +3022,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>10.681</v>
+        <v>10.865</v>
       </c>
     </row>
     <row r="160">
@@ -3037,7 +3040,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>34.8</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="161">
@@ -3127,7 +3130,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.663058039234257</v>
+        <v>0.7506167419386574</v>
       </c>
     </row>
     <row r="166"/>
@@ -3146,7 +3149,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>13.2090602999694</v>
+        <v>12.69972451790634</v>
       </c>
     </row>
     <row r="168">
@@ -3164,7 +3167,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10.99326599326599</v>
+        <v>11.32614018977655</v>
       </c>
     </row>
     <row r="169">
@@ -3182,7 +3185,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>87.94</v>
+        <v>69.572</v>
       </c>
     </row>
     <row r="170">
@@ -3200,7 +3203,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10.865</v>
+        <v>11.1845</v>
       </c>
     </row>
     <row r="171">
@@ -3218,7 +3221,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>46.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="172">
@@ -3308,7 +3311,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1.120816690478747</v>
+        <v>0.8185260062549369</v>
       </c>
     </row>
     <row r="177"/>
@@ -3327,7 +3330,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10.66666666666667</v>
+        <v>10.996996996997</v>
       </c>
     </row>
     <row r="179">
@@ -3345,7 +3348,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>12.77777777777778</v>
+        <v>12.8328328328328</v>
       </c>
     </row>
     <row r="180">
@@ -3363,7 +3366,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>34.09200000000001</v>
+        <v>37.652</v>
       </c>
     </row>
     <row r="181">
@@ -3381,7 +3384,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>12.615</v>
+        <v>12.667</v>
       </c>
     </row>
     <row r="182">
@@ -3399,7 +3402,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>31</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="183">
@@ -3489,7 +3492,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.758461637891148</v>
+        <v>1.555671174145813</v>
       </c>
     </row>
     <row r="188"/>
@@ -3508,7 +3511,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>13.14222222222222</v>
+        <v>11.3406795224977</v>
       </c>
     </row>
     <row r="190">
@@ -3526,7 +3529,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11.73055555555555</v>
+        <v>12.88950107131926</v>
       </c>
     </row>
     <row r="191">
@@ -3544,7 +3547,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>85.559</v>
+        <v>41.992</v>
       </c>
     </row>
     <row r="192">
@@ -3562,7 +3565,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11.5845</v>
+        <v>12.708</v>
       </c>
     </row>
     <row r="193">
@@ -3580,7 +3583,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>45.4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="194">
@@ -3670,7 +3673,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1.075549993587398</v>
+        <v>1.194107565967697</v>
       </c>
     </row>
     <row r="199"/>
@@ -3689,7 +3692,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>13.2090602999694</v>
+        <v>11.738579045972</v>
       </c>
     </row>
     <row r="201">
@@ -3707,7 +3710,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>10.99326599326599</v>
+        <v>12.45064130278138</v>
       </c>
     </row>
     <row r="202">
@@ -3725,7 +3728,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>87.94</v>
+        <v>48.132</v>
       </c>
     </row>
     <row r="203">
@@ -3743,7 +3746,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>10.865</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="204">
@@ -3761,7 +3764,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>46.8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="205">
@@ -3851,7 +3854,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1.317127809106402</v>
+        <v>0.9756657495634642</v>
       </c>
     </row>
     <row r="210"/>
@@ -3870,7 +3873,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>11.16478797638218</v>
+        <v>12.58141160027952</v>
       </c>
     </row>
     <row r="212">
@@ -3888,7 +3891,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>10.51485059939166</v>
+        <v>12.54454926624738</v>
       </c>
     </row>
     <row r="213">
@@ -3906,7 +3909,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>39.732</v>
+        <v>66.07199999999999</v>
       </c>
     </row>
     <row r="214">
@@ -3924,7 +3927,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>10.387</v>
+        <v>12.3715</v>
       </c>
     </row>
     <row r="215">
@@ -3942,7 +3945,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>36</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="216">
@@ -4032,7 +4035,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2.736569462345846</v>
+        <v>0.6865033701235107</v>
       </c>
     </row>
     <row r="221"/>
@@ -4051,7 +4054,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>12.58141160027952</v>
+        <v>12.2357850808555</v>
       </c>
     </row>
     <row r="223">
@@ -4069,7 +4072,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>12.54454926624738</v>
+        <v>11.64058424621805</v>
       </c>
     </row>
     <row r="224">
@@ -4087,7 +4090,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>66.07199999999999</v>
+        <v>57.612</v>
       </c>
     </row>
     <row r="225">
@@ -4105,7 +4108,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>12.3715</v>
+        <v>11.4995</v>
       </c>
     </row>
     <row r="226">
@@ -4123,7 +4126,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>51.8</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="227">
@@ -4213,7 +4216,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.5739778505623863</v>
+        <v>0.7422266782143664</v>
       </c>
     </row>
     <row r="232"/>
@@ -4232,7 +4235,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>10.996996996997</v>
+        <v>12.7468671679198</v>
       </c>
     </row>
     <row r="234">
@@ -4250,7 +4253,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>12.8328328328328</v>
+        <v>10.97257031467558</v>
       </c>
     </row>
     <row r="235">
@@ -4268,7 +4271,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>37.652</v>
+        <v>71.04000000000001</v>
       </c>
     </row>
     <row r="236">
@@ -4286,7 +4289,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>12.667</v>
+        <v>10.842</v>
       </c>
     </row>
     <row r="237">
@@ -4304,7 +4307,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>36.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="238">
@@ -4394,7 +4397,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1.760489089661558</v>
+        <v>0.7235868624159197</v>
       </c>
     </row>
     <row r="243"/>
@@ -4413,7 +4416,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>11.3406795224977</v>
+        <v>12.15440329218107</v>
       </c>
     </row>
     <row r="245">
@@ -4431,7 +4434,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>12.88950107131926</v>
+        <v>12.48312757201646</v>
       </c>
     </row>
     <row r="246">
@@ -4449,7 +4452,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>41.992</v>
+        <v>55.852</v>
       </c>
     </row>
     <row r="247">
@@ -4467,7 +4470,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>12.708</v>
+        <v>12.3195</v>
       </c>
     </row>
     <row r="248">
@@ -4485,7 +4488,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>43</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="249">
@@ -4575,7 +4578,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>2.035027441707895</v>
+        <v>0.6113235944518974</v>
       </c>
     </row>
     <row r="254"/>
@@ -4594,7 +4597,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>12.63108778069408</v>
+        <v>11.16478797638218</v>
       </c>
     </row>
     <row r="256">
@@ -4612,7 +4615,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>12.10411198600175</v>
+        <v>10.51485059939166</v>
       </c>
     </row>
     <row r="257">
@@ -4630,7 +4633,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>67.572</v>
+        <v>39.732</v>
       </c>
     </row>
     <row r="258">
@@ -4648,7 +4651,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>11.95</v>
+        <v>10.387</v>
       </c>
     </row>
     <row r="259">
@@ -4666,7 +4669,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>45.6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="260">
@@ -4756,7 +4759,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.7128854175182557</v>
+        <v>1.372952671113548</v>
       </c>
     </row>
     <row r="265"/>
@@ -4775,7 +4778,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>11.7109144542773</v>
+        <v>11.1318832059573</v>
       </c>
     </row>
     <row r="267">
@@ -4793,7 +4796,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>12.9203539823009</v>
+        <v>10.8441113070743</v>
       </c>
     </row>
     <row r="268">
@@ -4811,7 +4814,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>47.472</v>
+        <v>39.27200000000001</v>
       </c>
     </row>
     <row r="269">
@@ -4829,7 +4832,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>12.7325</v>
+        <v>10.723</v>
       </c>
     </row>
     <row r="270">
@@ -4847,7 +4850,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>50.4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="271">
@@ -4937,7 +4940,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1.203150271218366</v>
+        <v>1.123627274237862</v>
       </c>
     </row>
     <row r="276"/>
@@ -4956,7 +4959,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>12.54716981132075</v>
+        <v>13.14222222222222</v>
       </c>
     </row>
     <row r="278">
@@ -4974,7 +4977,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>13.01712089447939</v>
+        <v>11.73055555555555</v>
       </c>
     </row>
     <row r="279">
@@ -4992,7 +4995,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>65.13199999999999</v>
+        <v>85.559</v>
       </c>
     </row>
     <row r="280">
@@ -5010,7 +5013,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>12.8285</v>
+        <v>11.5845</v>
       </c>
     </row>
     <row r="281">
@@ -5028,7 +5031,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>55.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="282">
@@ -5118,7 +5121,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1.525262910179049</v>
+        <v>0.8071590972249139</v>
       </c>
     </row>
     <row r="287"/>
@@ -5137,7 +5140,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>12.69972451790634</v>
+        <v>12.27751695357329</v>
       </c>
     </row>
     <row r="289">
@@ -5155,7 +5158,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>11.32614018977655</v>
+        <v>11.2754303599374</v>
       </c>
     </row>
     <row r="290">
@@ -5173,7 +5176,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>69.572</v>
+        <v>58.492</v>
       </c>
     </row>
     <row r="291">
@@ -5191,7 +5194,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>11.1845</v>
+        <v>11.1425</v>
       </c>
     </row>
     <row r="292">
@@ -5209,7 +5212,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>45.6</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="293">
@@ -5299,7 +5302,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.894232475925651</v>
+        <v>0.7502793689705489</v>
       </c>
     </row>
     <row r="298"/>
@@ -5318,7 +5321,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>12.124326970142</v>
+        <v>11.4428341384863</v>
       </c>
     </row>
     <row r="300">
@@ -5336,7 +5339,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>12.9548050252896</v>
+        <v>11.5901771336554</v>
       </c>
     </row>
     <row r="301">
@@ -5354,7 +5357,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>55.092</v>
+        <v>43.392</v>
       </c>
     </row>
     <row r="302">
@@ -5372,7 +5375,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>12.767</v>
+        <v>11.444</v>
       </c>
     </row>
     <row r="303">
@@ -5390,7 +5393,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>51.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="304">
@@ -5480,7 +5483,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1.163272556017446</v>
+        <v>0.8827992328642806</v>
       </c>
     </row>
     <row r="309"/>
@@ -5499,7 +5502,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>13.14222222222222</v>
+        <v>11.1318832059573</v>
       </c>
     </row>
     <row r="311">
@@ -5517,7 +5520,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>11.73055555555555</v>
+        <v>10.8441113070743</v>
       </c>
     </row>
     <row r="312">
@@ -5535,7 +5538,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>85.559</v>
+        <v>39.27200000000001</v>
       </c>
     </row>
     <row r="313">
@@ -5553,7 +5556,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>11.5845</v>
+        <v>10.723</v>
       </c>
     </row>
     <row r="314">
@@ -5571,7 +5574,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>45.4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="315">
@@ -5661,7 +5664,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1.455191336085227</v>
+        <v>1.116859255269899</v>
       </c>
     </row>
     <row r="320"/>
@@ -5680,7 +5683,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>11.041366041366</v>
+        <v>11.16478797638218</v>
       </c>
     </row>
     <row r="322">
@@ -5698,7 +5701,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>11.9450456950457</v>
+        <v>10.51485059939166</v>
       </c>
     </row>
     <row r="323">
@@ -5716,7 +5719,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>38.11199999999999</v>
+        <v>39.732</v>
       </c>
     </row>
     <row r="324">
@@ -5734,7 +5737,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>11.806</v>
+        <v>10.387</v>
       </c>
     </row>
     <row r="325">
@@ -5752,7 +5755,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>36.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="326">
@@ -5842,7 +5845,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.3954310506702687</v>
+        <v>1.358706282513382</v>
       </c>
     </row>
     <row r="331"/>
@@ -5861,7 +5864,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>11.77062579821201</v>
+        <v>10.68640266564142</v>
       </c>
     </row>
     <row r="333">
@@ -5879,7 +5882,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>12.01596424010217</v>
+        <v>12.33371780084583</v>
       </c>
     </row>
     <row r="334">
@@ -5897,7 +5900,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>48.572</v>
+        <v>34.192</v>
       </c>
     </row>
     <row r="335">
@@ -5915,7 +5918,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>11.864</v>
+        <v>12.1655</v>
       </c>
     </row>
     <row r="336">
@@ -5933,7 +5936,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>41.8</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="337">
@@ -6023,7 +6026,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.2579288019940448</v>
+        <v>1.480069803403029</v>
       </c>
     </row>
     <row r="342"/>
@@ -6042,7 +6045,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>11.5321740838982</v>
+        <v>12.65441819772528</v>
       </c>
     </row>
     <row r="344">
@@ -6060,7 +6063,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>10.5432753708616</v>
+        <v>11.69582968795567</v>
       </c>
     </row>
     <row r="345">
@@ -6078,7 +6081,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>44.755</v>
+        <v>68.152</v>
       </c>
     </row>
     <row r="346">
@@ -6096,7 +6099,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>10.4155</v>
+        <v>11.547</v>
       </c>
     </row>
     <row r="347">
@@ -6114,7 +6117,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="348">
@@ -6204,7 +6207,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>2.782411182798814</v>
+        <v>0.7382295191576398</v>
       </c>
     </row>
     <row r="353"/>
@@ -6223,7 +6226,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>10.76866395191003</v>
+        <v>10.82486662027372</v>
       </c>
     </row>
     <row r="355">
@@ -6241,7 +6244,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>11.14989334884623</v>
+        <v>10.48248666202737</v>
       </c>
     </row>
     <row r="356">
@@ -6259,7 +6262,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>35.072</v>
+        <v>35.712</v>
       </c>
     </row>
     <row r="357">
@@ -6277,7 +6280,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>11.017</v>
+        <v>10.3635</v>
       </c>
     </row>
     <row r="358">
@@ -6295,7 +6298,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>33.6</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="359">
@@ -6385,7 +6388,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2.829822503848865</v>
+        <v>1.733242435683321</v>
       </c>
     </row>
     <row r="364"/>
@@ -6404,7 +6407,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>10.996996996997</v>
+        <v>11.5321740838982</v>
       </c>
     </row>
     <row r="366">
@@ -6422,7 +6425,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>12.8328328328328</v>
+        <v>10.5432753708616</v>
       </c>
     </row>
     <row r="367">
@@ -6440,7 +6443,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>37.652</v>
+        <v>44.755</v>
       </c>
     </row>
     <row r="368">
@@ -6458,7 +6461,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>12.667</v>
+        <v>10.4155</v>
       </c>
     </row>
     <row r="369">
@@ -6476,7 +6479,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>36.8</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="370">
@@ -6566,7 +6569,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1.760489089661558</v>
+        <v>1.19134248516953</v>
       </c>
     </row>
     <row r="375"/>
@@ -6585,7 +6588,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>13.2090602999694</v>
+        <v>12.63108778069408</v>
       </c>
     </row>
     <row r="377">
@@ -6603,7 +6606,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>10.99326599326599</v>
+        <v>12.10411198600175</v>
       </c>
     </row>
     <row r="378">
@@ -6621,7 +6624,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>87.94</v>
+        <v>67.572</v>
       </c>
     </row>
     <row r="379">
@@ -6639,7 +6642,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>10.865</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="380">
@@ -6657,7 +6660,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>46.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="381">
@@ -6747,7 +6750,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1.692071800929237</v>
+        <v>0.7045807631628008</v>
       </c>
     </row>
     <row r="386"/>
@@ -6766,7 +6769,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>11.8576306803257</v>
+        <v>10.70518518518519</v>
       </c>
     </row>
     <row r="388">
@@ -6784,7 +6787,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>11.24573154715</v>
+        <v>11.91111111111111</v>
       </c>
     </row>
     <row r="389">
@@ -6802,7 +6805,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>50.212</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="390">
@@ -6820,7 +6823,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>11.11</v>
+        <v>11.767</v>
       </c>
     </row>
     <row r="391">
@@ -6838,7 +6841,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>36.2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="392">
@@ -6928,7 +6931,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.7232649457968846</v>
+        <v>1.466474472587644</v>
       </c>
     </row>
     <row r="397"/>
@@ -6947,7 +6950,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>13.17441077441077</v>
+        <v>10.79717813051146</v>
       </c>
     </row>
     <row r="399">
@@ -6965,7 +6968,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>11.35185185185185</v>
+        <v>10.81128747795414</v>
       </c>
     </row>
     <row r="400">
@@ -6983,7 +6986,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>86.45999999999999</v>
+        <v>35.372</v>
       </c>
     </row>
     <row r="401">
@@ -7001,7 +7004,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>11.214</v>
+        <v>10.681</v>
       </c>
     </row>
     <row r="402">
@@ -7019,7 +7022,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>47.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="403">
@@ -7109,7 +7112,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1.31414427250139</v>
+        <v>1.580127146234471</v>
       </c>
     </row>
     <row r="408"/>
@@ -7128,7 +7131,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>12.124326970142</v>
+        <v>11.1033138401559</v>
       </c>
     </row>
     <row r="410">
@@ -7146,7 +7149,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>12.9548050252896</v>
+        <v>11.1842105263158</v>
       </c>
     </row>
     <row r="411">
@@ -7164,7 +7167,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>55.092</v>
+        <v>38.852</v>
       </c>
     </row>
     <row r="412">
@@ -7182,7 +7185,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>12.767</v>
+        <v>11.0445</v>
       </c>
     </row>
     <row r="413">
@@ -7200,7 +7203,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>51.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="414">
@@ -7290,7 +7293,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1.073980218886957</v>
+        <v>0.975403262376725</v>
       </c>
     </row>
     <row r="419"/>
@@ -7309,7 +7312,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>12.27751695357329</v>
+        <v>11.8576306803257</v>
       </c>
     </row>
     <row r="421">
@@ -7327,7 +7330,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>11.2754303599374</v>
+        <v>11.24573154715</v>
       </c>
     </row>
     <row r="422">
@@ -7345,7 +7348,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>58.492</v>
+        <v>50.212</v>
       </c>
     </row>
     <row r="423">
@@ -7363,7 +7366,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>11.1425</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="424">
@@ -7381,7 +7384,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>41.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="425">
@@ -7471,7 +7474,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>0.3968039656360116</v>
+        <v>0.7535042795537336</v>
       </c>
     </row>
     <row r="430"/>
@@ -7490,7 +7493,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>13.2090602999694</v>
+        <v>13.17441077441077</v>
       </c>
     </row>
     <row r="432">
@@ -7508,7 +7511,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>10.99326599326599</v>
+        <v>11.35185185185185</v>
       </c>
     </row>
     <row r="433">
@@ -7526,7 +7529,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>87.94</v>
+        <v>86.45999999999999</v>
       </c>
     </row>
     <row r="434">
@@ -7544,7 +7547,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>10.865</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="435">
@@ -7562,7 +7565,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>46.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="436">
@@ -7652,7 +7655,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1.712266151838323</v>
+        <v>0.7707121456008711</v>
       </c>
     </row>
     <row r="441"/>
@@ -7671,7 +7674,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>13.27609427609428</v>
+        <v>11.402809706258</v>
       </c>
     </row>
     <row r="443">
@@ -7689,7 +7692,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>10.65656565656566</v>
+        <v>11.9904214559387</v>
       </c>
     </row>
     <row r="444">
@@ -7707,7 +7710,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>91.16</v>
+        <v>42.852</v>
       </c>
     </row>
     <row r="445">
@@ -7725,7 +7728,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>10.5375</v>
+        <v>11.8385</v>
       </c>
     </row>
     <row r="446">
@@ -7743,7 +7746,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>42.4</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="447">
@@ -7833,7 +7836,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1.698231941427746</v>
+        <v>0.9222891344103304</v>
       </c>
     </row>
     <row r="452"/>
@@ -7852,7 +7855,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>10.996996996997</v>
+        <v>11.3696498054475</v>
       </c>
     </row>
     <row r="454">
@@ -7870,7 +7873,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>12.8328328328328</v>
+        <v>12.4218187058654</v>
       </c>
     </row>
     <row r="455">
@@ -7888,7 +7891,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>37.652</v>
+        <v>42.452</v>
       </c>
     </row>
     <row r="456">
@@ -7906,7 +7909,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>12.667</v>
+        <v>12.256</v>
       </c>
     </row>
     <row r="457">
@@ -7924,7 +7927,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>36.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="458">
@@ -8014,7 +8017,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>2.288635816560026</v>
+        <v>0.8002034232189694</v>
       </c>
     </row>
     <row r="463"/>
@@ -8033,7 +8036,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>12.79142300194932</v>
+        <v>11.7109144542773</v>
       </c>
     </row>
     <row r="465">
@@ -8051,7 +8054,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>10.63840155945419</v>
+        <v>12.9203539823009</v>
       </c>
     </row>
     <row r="466">
@@ -8069,7 +8072,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>72.23999999999999</v>
+        <v>47.472</v>
       </c>
     </row>
     <row r="467">
@@ -8087,7 +8090,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>10.5175</v>
+        <v>12.7325</v>
       </c>
     </row>
     <row r="468">
@@ -8105,7 +8108,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>43</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="469">
@@ -8195,7 +8198,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2.230211918388463</v>
+        <v>1.025556000885823</v>
       </c>
     </row>
     <row r="474"/>
@@ -8214,7 +8217,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>10.73763816172193</v>
+        <v>12.33154533844189</v>
       </c>
     </row>
     <row r="476">
@@ -8232,7 +8235,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>11.51832460732984</v>
+        <v>10.59323116219668</v>
       </c>
     </row>
     <row r="477">
@@ -8250,7 +8253,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>34.752</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="478">
@@ -8268,7 +8271,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>11.38</v>
+        <v>10.4625</v>
       </c>
     </row>
     <row r="479">
@@ -8286,7 +8289,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>33</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="480">
@@ -8376,7 +8379,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>2.609771845929499</v>
+        <v>0.986336117426784</v>
       </c>
     </row>
     <row r="485"/>
@@ -8395,7 +8398,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>12.58141160027952</v>
+        <v>12.79142300194932</v>
       </c>
     </row>
     <row r="487">
@@ -8413,7 +8416,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>12.54454926624738</v>
+        <v>10.63840155945419</v>
       </c>
     </row>
     <row r="488">
@@ -8431,7 +8434,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>66.07199999999999</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="489">
@@ -8449,7 +8452,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>12.3715</v>
+        <v>10.5175</v>
       </c>
     </row>
     <row r="490">
@@ -8467,7 +8470,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>51.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="491">
@@ -8557,7 +8560,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>0.7478863810237479</v>
+        <v>0.9977298819880317</v>
       </c>
     </row>
     <row r="496"/>
@@ -8576,7 +8579,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>12.54716981132075</v>
+        <v>10.66666666666667</v>
       </c>
     </row>
     <row r="498">
@@ -8594,7 +8597,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>13.01712089447939</v>
+        <v>12.77777777777778</v>
       </c>
     </row>
     <row r="499">
@@ -8612,7 +8615,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>65.13199999999999</v>
+        <v>34.09200000000001</v>
       </c>
     </row>
     <row r="500">
@@ -8630,7 +8633,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>12.8285</v>
+        <v>12.615</v>
       </c>
     </row>
     <row r="501">
@@ -8648,7 +8651,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>55.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="502">
@@ -8738,7 +8741,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1.217224567513557</v>
+        <v>2.076479109600597</v>
       </c>
     </row>
     <row r="507"/>
@@ -8757,7 +8760,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>12.15440329218107</v>
+        <v>12.124326970142</v>
       </c>
     </row>
     <row r="509">
@@ -8775,7 +8778,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>12.48312757201646</v>
+        <v>12.9548050252896</v>
       </c>
     </row>
     <row r="510">
@@ -8793,7 +8796,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>55.852</v>
+        <v>55.092</v>
       </c>
     </row>
     <row r="511">
@@ -8811,7 +8814,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>12.3195</v>
+        <v>12.767</v>
       </c>
     </row>
     <row r="512">
@@ -8829,7 +8832,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>43.6</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="513">
@@ -8919,7 +8922,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>0.3994550179280869</v>
+        <v>0.8834954943305386</v>
       </c>
     </row>
     <row r="518"/>
@@ -8938,7 +8941,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>12.65441819772528</v>
+        <v>12.54716981132075</v>
       </c>
     </row>
     <row r="520">
@@ -8956,7 +8959,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>11.69582968795567</v>
+        <v>13.01712089447939</v>
       </c>
     </row>
     <row r="521">
@@ -8974,7 +8977,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>68.152</v>
+        <v>65.13199999999999</v>
       </c>
     </row>
     <row r="522">
@@ -8992,7 +8995,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>11.547</v>
+        <v>12.8285</v>
       </c>
     </row>
     <row r="523">
@@ -9010,7 +9013,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="524">
@@ -9100,7 +9103,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>0.8193309975383747</v>
+        <v>0.8190684294069043</v>
       </c>
     </row>
     <row r="529"/>
@@ -9119,7 +9122,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>12.69972451790634</v>
+        <v>10.73763816172193</v>
       </c>
     </row>
     <row r="531">
@@ -9137,7 +9140,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>11.32614018977655</v>
+        <v>11.51832460732984</v>
       </c>
     </row>
     <row r="532">
@@ -9155,7 +9158,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>69.572</v>
+        <v>34.752</v>
       </c>
     </row>
     <row r="533">
@@ -9173,7 +9176,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>11.1845</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="534">
@@ -9191,7 +9194,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>45.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="535">
@@ -9281,7 +9284,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>0.5891630646873236</v>
+        <v>1.501993649794463</v>
       </c>
     </row>
   </sheetData>
